--- a/tests/workbooktests/workbooks/test_exercise.xlsx
+++ b/tests/workbooktests/workbooks/test_exercise.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3EA6CE-C62A-4368-94F1-F2223A23D98A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10880946-5D44-4F8E-94E3-8B4E684314BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7065" yWindow="-20310" windowWidth="21330" windowHeight="15900" xr2:uid="{30D9BE8D-5392-49D4-9986-3F013E1F81B4}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{30D9BE8D-5392-49D4-9986-3F013E1F81B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -513,36 +513,36 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" cm="1">
-        <f t="array" ref="A4">_xll.qlCalendarAdvance2("NullCalendar",A3,"1M")</f>
-        <v>46204</v>
+      <c r="A4" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="A4" ca="1">_xll.qlCalendarAdvance2("NullCalendar",A3,"1M")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B4">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" cm="1">
-        <f t="array" ref="A5">_xll.qlCalendarAdvance2("NullCalendar",A4,"1M")</f>
-        <v>46235</v>
+      <c r="A5" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="A5" ca="1">_xll.qlCalendarAdvance2("NullCalendar",A4,"1M")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B5">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" cm="1">
-        <f t="array" ref="A6">_xll.qlCalendarAdvance2("NullCalendar",A5,"1M")</f>
-        <v>46266</v>
+      <c r="A6" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="A6" ca="1">_xll.qlCalendarAdvance2("NullCalendar",A5,"1M")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B6">
         <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" cm="1">
-        <f t="array" ref="A7">_xll.qlCalendarAdvance2("NullCalendar",A6,"1M")</f>
-        <v>46296</v>
+      <c r="A7" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="A7" ca="1">_xll.qlCalendarAdvance2("NullCalendar",A6,"1M")</f>
+        <v>#VALUE!</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -597,42 +597,33 @@
       <c r="A14" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="1" t="str" cm="1">
-        <f t="array" ref="B14">_xll.qlEuropeanExercise(A4)</f>
-        <v>⚡[test_exercise.xlsx]Sheet1!R14C2EuropeanExercise,A</v>
-      </c>
-      <c r="C14" t="str" cm="1">
-        <f t="array" ref="C14">_xll.qlExerciseType(B14)</f>
-        <v>EUROPEAN</v>
-      </c>
-      <c r="D14" s="1" cm="1">
-        <f t="array" ref="D14">_xll.qlExerciseDate(B14,0)</f>
-        <v>46204</v>
-      </c>
-      <c r="E14" cm="1">
-        <f t="array" ref="E14">_xll.qlExerciseDate(B14,1)</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="1" cm="1">
-        <f t="array" ref="F14">_xll.qlExerciseDateAt(B14,0)</f>
-        <v>46204</v>
-      </c>
-      <c r="G14" t="str" cm="1">
-        <f t="array" ref="G14">_xll.qlExerciseDateAt(B14,1)</f>
-        <v xml:space="preserve">IndexError: IndexError: invalid vector subscript
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlib_xloil\exercise.py", line 59, in qlExerciseDateAt
-    return exercise.dateAt(idx)
-           ~~~~~~~~~~~~~~~^^^^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 15448, in dateAt
-    return _QuantLib.Exercise_dateAt(self, index)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^^^^^^^^
-IndexError: invalid vector subscript
-</v>
-      </c>
-      <c r="H14" s="1" cm="1">
-        <f t="array" ref="H14">TRANSPOSE(_xll.qlExerciseDates(B14))</f>
-        <v>46204</v>
+      <c r="B14" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="B14" ca="1">_xll.qlEuropeanExercise(A4)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C14" t="e" cm="1">
+        <f t="array" aca="1" ref="C14" ca="1">_xll.qlExerciseType(B14)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D14" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="D14" ca="1">_xll.qlExerciseDate(B14,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E14" t="e" cm="1">
+        <f t="array" aca="1" ref="E14" ca="1">_xll.qlExerciseDate(B14,1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F14" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="F14" ca="1">_xll.qlExerciseDateAt(B14,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G14" t="e" cm="1">
+        <f t="array" aca="1" ref="G14" ca="1">FIND("IndexError: IndexError: invalid vector subscript",_xll.qlExerciseDateAt(B14,1))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H14" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="H14" ca="1">TRANSPOSE(_xll.qlExerciseDates(B14))</f>
+        <v>#VALUE!</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -643,82 +634,72 @@
       <c r="A15" t="s">
         <v>2</v>
       </c>
-      <c r="B15" t="str" cm="1">
-        <f t="array" ref="B15">_xll.qlBermudanExercise(A3:A7)</f>
-        <v>⚡[test_exercise.xlsx]Sheet1!R15C2BermudanExercise,A</v>
-      </c>
-      <c r="C15" t="str" cm="1">
-        <f t="array" ref="C15">_xll.qlExerciseType(B15)</f>
-        <v>BERMUDAN</v>
-      </c>
-      <c r="D15" s="1" cm="1">
-        <f t="array" ref="D15">_xll.qlExerciseDate(B15,0)</f>
-        <v>46174</v>
-      </c>
-      <c r="E15" s="1" cm="1">
-        <f t="array" ref="E15">_xll.qlExerciseDate(B15,1)</f>
-        <v>46204</v>
-      </c>
-      <c r="F15" s="1" cm="1">
-        <f t="array" ref="F15">_xll.qlExerciseDateAt(B15,0)</f>
-        <v>46174</v>
-      </c>
-      <c r="G15" s="1" cm="1">
-        <f t="array" ref="G15">_xll.qlExerciseDateAt(B15,1)</f>
-        <v>46204</v>
-      </c>
-      <c r="H15" s="1" cm="1">
-        <f t="array" ref="H15:L15">TRANSPOSE(_xll.qlExerciseDates(B15))</f>
-        <v>46174</v>
-      </c>
-      <c r="I15" s="1">
-        <v>46204</v>
-      </c>
-      <c r="J15" s="1">
-        <v>46235</v>
-      </c>
-      <c r="K15" s="1">
-        <v>46266</v>
-      </c>
-      <c r="L15" s="1">
-        <v>46296</v>
-      </c>
+      <c r="B15" t="e" cm="1">
+        <f t="array" aca="1" ref="B15" ca="1">_xll.qlBermudanExercise(A3:A7)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C15" t="e" cm="1">
+        <f t="array" aca="1" ref="C15" ca="1">_xll.qlExerciseType(B15)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D15" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="D15" ca="1">_xll.qlExerciseDate(B15,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E15" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="E15" ca="1">_xll.qlExerciseDate(B15,1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F15" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="F15" ca="1">_xll.qlExerciseDateAt(B15,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G15" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="G15" ca="1">_xll.qlExerciseDateAt(B15,1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H15" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="H15" ca="1">TRANSPOSE(_xll.qlExerciseDates(B15))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
-      <c r="B16" t="str" cm="1">
-        <f t="array" ref="B16">_xll.qlAmericanExercise(A3,A7)</f>
-        <v>⚡[test_exercise.xlsx]Sheet1!R16C2AmericanExercise,A</v>
-      </c>
-      <c r="C16" t="str" cm="1">
-        <f t="array" ref="C16">_xll.qlExerciseType(B16)</f>
-        <v>AMERICAN</v>
-      </c>
-      <c r="D16" s="1" cm="1">
-        <f t="array" ref="D16">_xll.qlExerciseDate(B16,0)</f>
-        <v>46174</v>
-      </c>
-      <c r="E16" s="1" cm="1">
-        <f t="array" ref="E16">_xll.qlExerciseDate(B16,1)</f>
-        <v>46296</v>
-      </c>
-      <c r="F16" s="1" cm="1">
-        <f t="array" ref="F16">_xll.qlExerciseDateAt(B16,0)</f>
-        <v>46174</v>
-      </c>
-      <c r="G16" s="1" cm="1">
-        <f t="array" ref="G16">_xll.qlExerciseDateAt(B16,1)</f>
-        <v>46296</v>
-      </c>
-      <c r="H16" s="1" cm="1">
-        <f t="array" ref="H16:I16">TRANSPOSE(_xll.qlExerciseDates(B16))</f>
-        <v>46174</v>
-      </c>
-      <c r="I16" s="1">
-        <v>46296</v>
-      </c>
+      <c r="B16" t="e" cm="1">
+        <f t="array" aca="1" ref="B16" ca="1">_xll.qlAmericanExercise(A3,A7)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C16" t="e" cm="1">
+        <f t="array" aca="1" ref="C16" ca="1">_xll.qlExerciseType(B16)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D16" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="D16" ca="1">_xll.qlExerciseDate(B16,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E16" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="E16" ca="1">_xll.qlExerciseDate(B16,1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F16" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="F16" ca="1">_xll.qlExerciseDateAt(B16,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G16" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="G16" ca="1">_xll.qlExerciseDateAt(B16,1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H16" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="H16" ca="1">TRANSPOSE(_xll.qlExerciseDates(B16))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -727,91 +708,75 @@
       <c r="A17" t="s">
         <v>10</v>
       </c>
-      <c r="B17" t="str" cm="1">
-        <f t="array" ref="B17">_xll.qlRebatedExercise(B15,B3:B7,B9,B10,B11)</f>
-        <v>⚡[test_exercise.xlsx]Sheet1!R17C2RebatedExercise,A</v>
-      </c>
-      <c r="C17" t="str" cm="1">
-        <f t="array" ref="C17">_xll.qlExerciseType(B17)</f>
-        <v>BERMUDAN</v>
-      </c>
-      <c r="D17" s="1" cm="1">
-        <f t="array" ref="D17">_xll.qlExerciseDate(B17,0)</f>
-        <v>46174</v>
-      </c>
-      <c r="E17" s="1" cm="1">
-        <f t="array" ref="E17">_xll.qlExerciseDate(B17,1)</f>
-        <v>46204</v>
-      </c>
-      <c r="F17" s="1" cm="1">
-        <f t="array" ref="F17">_xll.qlExerciseDateAt(B17,0)</f>
-        <v>46174</v>
-      </c>
-      <c r="G17" s="1" cm="1">
-        <f t="array" ref="G17">_xll.qlExerciseDateAt(B17,1)</f>
-        <v>46204</v>
-      </c>
-      <c r="H17" s="1" cm="1">
-        <f t="array" ref="H17:L17">TRANSPOSE(_xll.qlExerciseDates(B17))</f>
-        <v>46174</v>
-      </c>
-      <c r="I17" s="1">
-        <v>46204</v>
-      </c>
-      <c r="J17" s="1">
-        <v>46235</v>
-      </c>
-      <c r="K17" s="1">
-        <v>46266</v>
-      </c>
-      <c r="L17" s="1">
-        <v>46296</v>
-      </c>
+      <c r="B17" t="e" cm="1">
+        <f t="array" aca="1" ref="B17" ca="1">_xll.qlRebatedExercise(B15,B3:B7,B9,B10,B11)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C17" t="e" cm="1">
+        <f t="array" aca="1" ref="C17" ca="1">_xll.qlExerciseType(B17)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D17" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="D17" ca="1">_xll.qlExerciseDate(B17,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E17" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="E17" ca="1">_xll.qlExerciseDate(B17,1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F17" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="F17" ca="1">_xll.qlExerciseDateAt(B17,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G17" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="G17" ca="1">_xll.qlExerciseDateAt(B17,1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H17" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="H17" ca="1">TRANSPOSE(_xll.qlExerciseDates(B17))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
-      <c r="B18" t="str" cm="1">
-        <f t="array" ref="B18">_xll.qlSwingExercise(A3:A7)</f>
-        <v>⚡[test_exercise.xlsx]Sheet1!R18C2SwingExercise,A</v>
-      </c>
-      <c r="C18" t="str" cm="1">
-        <f t="array" ref="C18">_xll.qlExerciseType(B18)</f>
-        <v>BERMUDAN</v>
-      </c>
-      <c r="D18" s="1" cm="1">
-        <f t="array" ref="D18">_xll.qlExerciseDate(B18,0)</f>
-        <v>46174</v>
-      </c>
-      <c r="E18" s="1" cm="1">
-        <f t="array" ref="E18">_xll.qlExerciseDate(B18,1)</f>
-        <v>46204</v>
-      </c>
-      <c r="F18" s="1" cm="1">
-        <f t="array" ref="F18">_xll.qlExerciseDateAt(B18,0)</f>
-        <v>46174</v>
-      </c>
-      <c r="G18" s="1" cm="1">
-        <f t="array" ref="G18">_xll.qlExerciseDateAt(B18,1)</f>
-        <v>46204</v>
-      </c>
-      <c r="H18" s="1" cm="1">
-        <f t="array" ref="H18:L18">TRANSPOSE(_xll.qlExerciseDates(B18))</f>
-        <v>46174</v>
-      </c>
-      <c r="I18" s="1">
-        <v>46204</v>
-      </c>
-      <c r="J18" s="1">
-        <v>46235</v>
-      </c>
-      <c r="K18" s="1">
-        <v>46266</v>
-      </c>
-      <c r="L18" s="1">
-        <v>46296</v>
-      </c>
+      <c r="B18" t="e" cm="1">
+        <f t="array" aca="1" ref="B18" ca="1">_xll.qlSwingExercise(A3:A7)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C18" t="e" cm="1">
+        <f t="array" aca="1" ref="C18" ca="1">_xll.qlExerciseType(B18)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D18" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="D18" ca="1">_xll.qlExerciseDate(B18,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="E18" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="E18" ca="1">_xll.qlExerciseDate(B18,1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F18" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="F18" ca="1">_xll.qlExerciseDateAt(B18,0)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="G18" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="G18" ca="1">_xll.qlExerciseDateAt(B18,1)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H18" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="H18" ca="1">TRANSPOSE(_xll.qlExerciseDates(B18))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tests/workbooktests/workbooks/test_exercise.xlsx
+++ b/tests/workbooktests/workbooks/test_exercise.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10880946-5D44-4F8E-94E3-8B4E684314BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0263AD-EFA5-4E92-956C-4B3C6FDCED9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{30D9BE8D-5392-49D4-9986-3F013E1F81B4}"/>
+    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{30D9BE8D-5392-49D4-9986-3F013E1F81B4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -513,36 +513,36 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="A4" ca="1">_xll.qlCalendarAdvance2("NullCalendar",A3,"1M")</f>
-        <v>#VALUE!</v>
+      <c r="A4" s="1" cm="1">
+        <f t="array" ref="A4">_xll.qlCalendarAdvance("NullCalendar",A3,"1M")</f>
+        <v>46204</v>
       </c>
       <c r="B4">
         <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="A5" ca="1">_xll.qlCalendarAdvance2("NullCalendar",A4,"1M")</f>
-        <v>#VALUE!</v>
+      <c r="A5" s="1" cm="1">
+        <f t="array" ref="A5">_xll.qlCalendarAdvance("NullCalendar",A4,"1M")</f>
+        <v>46235</v>
       </c>
       <c r="B5">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="A6" ca="1">_xll.qlCalendarAdvance2("NullCalendar",A5,"1M")</f>
-        <v>#VALUE!</v>
+      <c r="A6" s="1" cm="1">
+        <f t="array" ref="A6">_xll.qlCalendarAdvance("NullCalendar",A5,"1M")</f>
+        <v>46266</v>
       </c>
       <c r="B6">
         <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="A7" ca="1">_xll.qlCalendarAdvance2("NullCalendar",A6,"1M")</f>
-        <v>#VALUE!</v>
+      <c r="A7" s="1" cm="1">
+        <f t="array" ref="A7">_xll.qlCalendarAdvance("NullCalendar",A6,"1M")</f>
+        <v>46296</v>
       </c>
       <c r="B7">
         <v>100</v>
@@ -597,33 +597,33 @@
       <c r="A14" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="B14" ca="1">_xll.qlEuropeanExercise(A4)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C14" t="e" cm="1">
-        <f t="array" aca="1" ref="C14" ca="1">_xll.qlExerciseType(B14)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D14" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="D14" ca="1">_xll.qlExerciseDate(B14,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E14" t="e" cm="1">
-        <f t="array" aca="1" ref="E14" ca="1">_xll.qlExerciseDate(B14,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F14" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="F14" ca="1">_xll.qlExerciseDateAt(B14,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G14" t="e" cm="1">
-        <f t="array" aca="1" ref="G14" ca="1">FIND("IndexError: IndexError: invalid vector subscript",_xll.qlExerciseDateAt(B14,1))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H14" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="H14" ca="1">TRANSPOSE(_xll.qlExerciseDates(B14))</f>
-        <v>#VALUE!</v>
+      <c r="B14" s="1" t="str" cm="1">
+        <f t="array" ref="B14">_xll.qlEuropeanExercise(A4)</f>
+        <v>欣[test_exercise.xlsx]Sheet1!R14C2EuropeanExercise,A</v>
+      </c>
+      <c r="C14" t="str" cm="1">
+        <f t="array" ref="C14">_xll.qlExerciseType(B14)</f>
+        <v>EUROPEAN</v>
+      </c>
+      <c r="D14" s="1" cm="1">
+        <f t="array" ref="D14">_xll.qlExerciseDate(B14,0)</f>
+        <v>46204</v>
+      </c>
+      <c r="E14" cm="1">
+        <f t="array" ref="E14">_xll.qlExerciseDate(B14,1)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="1" cm="1">
+        <f t="array" ref="F14">_xll.qlExerciseDateAt(B14,0)</f>
+        <v>46204</v>
+      </c>
+      <c r="G14" cm="1">
+        <f t="array" ref="G14">FIND("IndexError: IndexError: invalid vector subscript",_xll.qlExerciseDateAt(B14,1))</f>
+        <v>1</v>
+      </c>
+      <c r="H14" s="1" cm="1">
+        <f t="array" ref="H14">TRANSPOSE(_xll.qlExerciseDates(B14))</f>
+        <v>46204</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -634,72 +634,82 @@
       <c r="A15" t="s">
         <v>2</v>
       </c>
-      <c r="B15" t="e" cm="1">
-        <f t="array" aca="1" ref="B15" ca="1">_xll.qlBermudanExercise(A3:A7)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C15" t="e" cm="1">
-        <f t="array" aca="1" ref="C15" ca="1">_xll.qlExerciseType(B15)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D15" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="D15" ca="1">_xll.qlExerciseDate(B15,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E15" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="E15" ca="1">_xll.qlExerciseDate(B15,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F15" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="F15" ca="1">_xll.qlExerciseDateAt(B15,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G15" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="G15" ca="1">_xll.qlExerciseDateAt(B15,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H15" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="H15" ca="1">TRANSPOSE(_xll.qlExerciseDates(B15))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
+      <c r="B15" t="str" cm="1">
+        <f t="array" ref="B15">_xll.qlBermudanExercise(A3:A7)</f>
+        <v>欣[test_exercise.xlsx]Sheet1!R15C2BermudanExercise,A</v>
+      </c>
+      <c r="C15" t="str" cm="1">
+        <f t="array" ref="C15">_xll.qlExerciseType(B15)</f>
+        <v>BERMUDAN</v>
+      </c>
+      <c r="D15" s="1" cm="1">
+        <f t="array" ref="D15">_xll.qlExerciseDate(B15,0)</f>
+        <v>46174</v>
+      </c>
+      <c r="E15" s="1" cm="1">
+        <f t="array" ref="E15">_xll.qlExerciseDate(B15,1)</f>
+        <v>46204</v>
+      </c>
+      <c r="F15" s="1" cm="1">
+        <f t="array" ref="F15">_xll.qlExerciseDateAt(B15,0)</f>
+        <v>46174</v>
+      </c>
+      <c r="G15" s="1" cm="1">
+        <f t="array" ref="G15">_xll.qlExerciseDateAt(B15,1)</f>
+        <v>46204</v>
+      </c>
+      <c r="H15" s="1" cm="1">
+        <f t="array" ref="H15:L15">TRANSPOSE(_xll.qlExerciseDates(B15))</f>
+        <v>46174</v>
+      </c>
+      <c r="I15" s="1">
+        <v>46204</v>
+      </c>
+      <c r="J15" s="1">
+        <v>46235</v>
+      </c>
+      <c r="K15" s="1">
+        <v>46266</v>
+      </c>
+      <c r="L15" s="1">
+        <v>46296</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
-      <c r="B16" t="e" cm="1">
-        <f t="array" aca="1" ref="B16" ca="1">_xll.qlAmericanExercise(A3,A7)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C16" t="e" cm="1">
-        <f t="array" aca="1" ref="C16" ca="1">_xll.qlExerciseType(B16)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D16" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="D16" ca="1">_xll.qlExerciseDate(B16,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E16" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="E16" ca="1">_xll.qlExerciseDate(B16,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F16" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="F16" ca="1">_xll.qlExerciseDateAt(B16,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G16" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="G16" ca="1">_xll.qlExerciseDateAt(B16,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H16" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="H16" ca="1">TRANSPOSE(_xll.qlExerciseDates(B16))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I16" s="1"/>
+      <c r="B16" t="str" cm="1">
+        <f t="array" ref="B16">_xll.qlAmericanExercise(A3,A7)</f>
+        <v>欣[test_exercise.xlsx]Sheet1!R16C2AmericanExercise,A</v>
+      </c>
+      <c r="C16" t="str" cm="1">
+        <f t="array" ref="C16">_xll.qlExerciseType(B16)</f>
+        <v>AMERICAN</v>
+      </c>
+      <c r="D16" s="1" cm="1">
+        <f t="array" ref="D16">_xll.qlExerciseDate(B16,0)</f>
+        <v>46174</v>
+      </c>
+      <c r="E16" s="1" cm="1">
+        <f t="array" ref="E16">_xll.qlExerciseDate(B16,1)</f>
+        <v>46296</v>
+      </c>
+      <c r="F16" s="1" cm="1">
+        <f t="array" ref="F16">_xll.qlExerciseDateAt(B16,0)</f>
+        <v>46174</v>
+      </c>
+      <c r="G16" s="1" cm="1">
+        <f t="array" ref="G16">_xll.qlExerciseDateAt(B16,1)</f>
+        <v>46296</v>
+      </c>
+      <c r="H16" s="1" cm="1">
+        <f t="array" ref="H16:I16">TRANSPOSE(_xll.qlExerciseDates(B16))</f>
+        <v>46174</v>
+      </c>
+      <c r="I16" s="1">
+        <v>46296</v>
+      </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -708,75 +718,91 @@
       <c r="A17" t="s">
         <v>10</v>
       </c>
-      <c r="B17" t="e" cm="1">
-        <f t="array" aca="1" ref="B17" ca="1">_xll.qlRebatedExercise(B15,B3:B7,B9,B10,B11)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C17" t="e" cm="1">
-        <f t="array" aca="1" ref="C17" ca="1">_xll.qlExerciseType(B17)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D17" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="D17" ca="1">_xll.qlExerciseDate(B17,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E17" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="E17" ca="1">_xll.qlExerciseDate(B17,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F17" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="F17" ca="1">_xll.qlExerciseDateAt(B17,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G17" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="G17" ca="1">_xll.qlExerciseDateAt(B17,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H17" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="H17" ca="1">TRANSPOSE(_xll.qlExerciseDates(B17))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
+      <c r="B17" t="str" cm="1">
+        <f t="array" ref="B17">_xll.qlRebatedExercise(B15,B3:B7,B9,B10,B11)</f>
+        <v>欣[test_exercise.xlsx]Sheet1!R17C2RebatedExercise,A</v>
+      </c>
+      <c r="C17" t="str" cm="1">
+        <f t="array" ref="C17">_xll.qlExerciseType(B17)</f>
+        <v>BERMUDAN</v>
+      </c>
+      <c r="D17" s="1" cm="1">
+        <f t="array" ref="D17">_xll.qlExerciseDate(B17,0)</f>
+        <v>46174</v>
+      </c>
+      <c r="E17" s="1" cm="1">
+        <f t="array" ref="E17">_xll.qlExerciseDate(B17,1)</f>
+        <v>46204</v>
+      </c>
+      <c r="F17" s="1" cm="1">
+        <f t="array" ref="F17">_xll.qlExerciseDateAt(B17,0)</f>
+        <v>46174</v>
+      </c>
+      <c r="G17" s="1" cm="1">
+        <f t="array" ref="G17">_xll.qlExerciseDateAt(B17,1)</f>
+        <v>46204</v>
+      </c>
+      <c r="H17" s="1" cm="1">
+        <f t="array" ref="H17:L17">TRANSPOSE(_xll.qlExerciseDates(B17))</f>
+        <v>46174</v>
+      </c>
+      <c r="I17" s="1">
+        <v>46204</v>
+      </c>
+      <c r="J17" s="1">
+        <v>46235</v>
+      </c>
+      <c r="K17" s="1">
+        <v>46266</v>
+      </c>
+      <c r="L17" s="1">
+        <v>46296</v>
+      </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>11</v>
       </c>
-      <c r="B18" t="e" cm="1">
-        <f t="array" aca="1" ref="B18" ca="1">_xll.qlSwingExercise(A3:A7)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C18" t="e" cm="1">
-        <f t="array" aca="1" ref="C18" ca="1">_xll.qlExerciseType(B18)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D18" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="D18" ca="1">_xll.qlExerciseDate(B18,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E18" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="E18" ca="1">_xll.qlExerciseDate(B18,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F18" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="F18" ca="1">_xll.qlExerciseDateAt(B18,0)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G18" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="G18" ca="1">_xll.qlExerciseDateAt(B18,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H18" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="H18" ca="1">TRANSPOSE(_xll.qlExerciseDates(B18))</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
+      <c r="B18" t="str" cm="1">
+        <f t="array" ref="B18">_xll.qlSwingExercise(A3:A7)</f>
+        <v>欣[test_exercise.xlsx]Sheet1!R18C2SwingExercise,A</v>
+      </c>
+      <c r="C18" t="str" cm="1">
+        <f t="array" ref="C18">_xll.qlExerciseType(B18)</f>
+        <v>BERMUDAN</v>
+      </c>
+      <c r="D18" s="1" cm="1">
+        <f t="array" ref="D18">_xll.qlExerciseDate(B18,0)</f>
+        <v>46174</v>
+      </c>
+      <c r="E18" s="1" cm="1">
+        <f t="array" ref="E18">_xll.qlExerciseDate(B18,1)</f>
+        <v>46204</v>
+      </c>
+      <c r="F18" s="1" cm="1">
+        <f t="array" ref="F18">_xll.qlExerciseDateAt(B18,0)</f>
+        <v>46174</v>
+      </c>
+      <c r="G18" s="1" cm="1">
+        <f t="array" ref="G18">_xll.qlExerciseDateAt(B18,1)</f>
+        <v>46204</v>
+      </c>
+      <c r="H18" s="1" cm="1">
+        <f t="array" ref="H18:L18">TRANSPOSE(_xll.qlExerciseDates(B18))</f>
+        <v>46174</v>
+      </c>
+      <c r="I18" s="1">
+        <v>46204</v>
+      </c>
+      <c r="J18" s="1">
+        <v>46235</v>
+      </c>
+      <c r="K18" s="1">
+        <v>46266</v>
+      </c>
+      <c r="L18" s="1">
+        <v>46296</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
